--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -1409,7 +1409,7 @@
         <v>9999</v>
       </c>
       <c r="K10" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2">
         <v>8</v>
@@ -1441,7 +1441,7 @@
         <v>9999</v>
       </c>
       <c r="K11" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2">
         <v>2</v>
@@ -1473,7 +1473,7 @@
         <v>9999</v>
       </c>
       <c r="K12" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2">
         <v>1</v>
@@ -1505,7 +1505,7 @@
         <v>9999</v>
       </c>
       <c r="K13" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2">
         <v>1</v>
@@ -1537,7 +1537,7 @@
         <v>9999</v>
       </c>
       <c r="K14" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2">
         <v>1</v>
@@ -1601,7 +1601,7 @@
         <v>100</v>
       </c>
       <c r="K16" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2">
         <v>1</v>
